--- a/doctool/test/auto/scenario12/レビュー記録サマリ_S12_expected.xlsx
+++ b/doctool/test/auto/scenario12/レビュー記録サマリ_S12_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EFF23B-9E2D-44EA-B2F3-021FC0F09441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEAD3FC-430E-427D-9FB8-9F9EA52E411F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9645" yWindow="4665" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,9 +711,6 @@
     <t>D00001</t>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S11</t>
-  </si>
-  <si>
     <t>鈴木　花子</t>
   </si>
   <si>
@@ -721,6 +718,10 @@
   </si>
   <si>
     <t>回覧</t>
+  </si>
+  <si>
+    <t>システム機能設計書_サンプル_S12</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1977,10 +1978,10 @@
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="44" t="s">
         <v>98</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>99</v>
       </c>
       <c r="H6" s="45">
         <v>1</v>
@@ -2008,7 +2009,7 @@
         <v>200</v>
       </c>
       <c r="Q6" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R6" s="53"/>
       <c r="S6" s="53"/>
@@ -2016,11 +2017,11 @@
       <c r="U6" s="53"/>
       <c r="V6" s="53"/>
       <c r="W6" s="54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X6" s="53"/>
       <c r="Y6" s="55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z6" s="56">
         <f t="shared" ref="Z6" si="1">IF(Y6="回覧",COUNTA(Q6:V6),COUNTA(Q6:X6))</f>
